--- a/elenco_locali.xlsx
+++ b/elenco_locali.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EA900083204R</t>
+          <t>EA570032568A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAR MULINO</t>
+          <t>AISHA'S CAFE'</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -453,29 +453,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA560077165A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BREAK BAR_NTS</t>
+          <t>AL BARILOTT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EA570008924W</t>
+          <t>EA570008867A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L'INSOLITO POSTO</t>
+          <t>AL CAFFERINO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -487,12 +487,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EA110058238S</t>
+          <t>EA580129846Q</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
+          <t>AL CHIOSCO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -504,80 +504,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EA110187005R</t>
+          <t>EA060105360R</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TABACCHERIA BACCO</t>
+          <t>ANG&amp;LY CAFFE'</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EA110057947A</t>
+          <t>EA060220578Q</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
+          <t>ARBA MARCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EA900083204R</t>
+          <t>EA610007856A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAR MULINO_NTS</t>
+          <t>ART CAFE' TABACCHERIA N. 2 - PRIVATIVA N. 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EA110071158R</t>
+          <t>EA190071960W</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAR TABACCHERIA EDEN</t>
+          <t>ASD MASTER POOL CLUB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EA110230333G</t>
+          <t>EA190071960W</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COFFEE STOP DI CHEN JIANYANG</t>
+          <t>ASD MASTER POOL CLUB_NTS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -589,63 +589,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EA110043088F</t>
+          <t>EA060229230A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TABACCHI DI CHEN MAOXI</t>
+          <t>ASSOCIAZIONE PROMOZIONE SOCIALE NUOVO LOLLI CLUB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Sisal Entertainment S.p.a.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EA570053989R</t>
+          <t>EA060229230A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EDEN BAR TABACCHI GELATERIA</t>
+          <t>ASSOCIAZIONE PROMOZIONE SOCIALE NUOVO LOLLI CLUB_NTS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EA110013463S</t>
+          <t>EA560050362R</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
+          <t>BAR 2 FANTI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EA560085800A</t>
+          <t>EA220084007M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAR VALLI</t>
+          <t>BAR AL BOSCHETTO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -657,12 +657,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EA910086595R</t>
+          <t>EA560022016R</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
+          <t>BAR BALISIO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EA570032568A</t>
+          <t>EA900206092R</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AISHA'S CAFE'</t>
+          <t>BAR BARAONDA DI JIN QINJING</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EA570011433R</t>
+          <t>EA560041556A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ULTIMA PRIMA BAR TABACCHI</t>
+          <t>BAR BARTH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -708,29 +708,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EA090004379E</t>
+          <t>EA610130067R</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
+          <t>BAR CAFFETTERIA DOC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EA230020700R</t>
+          <t>EA060084328R</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE_NTS</t>
+          <t>BAR CENTRALE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -742,46 +742,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EA230197328T</t>
+          <t>EA740137695R</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAR ORNELLA</t>
+          <t>BAR DEL PARCO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EA590018902R</t>
+          <t>EA580114981R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE_NTS</t>
+          <t>BAR EDEN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EA560077165A</t>
+          <t>EA580046885R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AL BARILOTT</t>
+          <t>BAR FIORI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -793,12 +793,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EA570047109R</t>
+          <t>EA570047692R</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BAR SPORT</t>
+          <t>BAR GELATERIA ECLISSE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EA560068687A</t>
+          <t>EA600009349R</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIRCOLO FRATELLI FIGINI</t>
+          <t>BAR HAVANA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,29 +827,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EA110086976R</t>
+          <t>EA910086595R</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI FRANCESCO SHI</t>
+          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EA230156447J</t>
+          <t>EA910086595R</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OSTERIA VENEZIA</t>
+          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -861,12 +861,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EA570132577S</t>
+          <t>EA110136204R</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
+          <t>BAR ITALIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -878,46 +878,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EA060228071B</t>
+          <t>EA230188759R</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISOLA C&amp;F SRL</t>
+          <t>BAR ITALIA (VE)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EA060087417R</t>
+          <t>EA600008487R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
+          <t>BAR ITALO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EA600145289K</t>
+          <t>EA610047253R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HAVANA SALA SLOT</t>
+          <t>BAR JOLLY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EA560037045R</t>
+          <t>EA570016040D</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAR SPORT (LC)</t>
+          <t>BAR LA POSTA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,29 +946,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EA230093288A</t>
+          <t>EA600012344R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA - NTS</t>
+          <t>BAR LE TORRI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EA910086595R</t>
+          <t>EA750192643R</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
+          <t>BAR M DI MELONI FRANCESCO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -980,46 +980,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EA060229233B</t>
+          <t>EA560024683A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ISOLA COFFE &amp; FOOD</t>
+          <t>BAR MANARA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EA230093288A</t>
+          <t>EA0600093414R</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA</t>
+          <t>BAR MARIO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EA580129846Q</t>
+          <t>EA010223483R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AL CHIOSCO</t>
+          <t>BAR MISSISSIPI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1031,29 +1031,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EA750225550C</t>
+          <t>EA900083204R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NEW BAR_NTS</t>
+          <t>BAR MULINO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EA750192643R</t>
+          <t>EA900083204R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BAR M DI MELONI FRANCESCO</t>
+          <t>BAR MULINO_NTS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1065,12 +1065,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EA010223483R</t>
+          <t>EA560014229R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BAR MISSISSIPI</t>
+          <t>BAR NORGE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EA580114981R</t>
+          <t>EA110026152R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BAR EDEN</t>
+          <t>BAR NUOVO MILLENNIO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EA570016040D</t>
+          <t>EA230093288A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BAR LA POSTA</t>
+          <t>BAR OMBRALONGA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1116,29 +1116,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EA110019632A</t>
+          <t>EA230093288A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI MARIO</t>
+          <t>BAR OMBRALONGA - NTS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EA230014587S</t>
+          <t>EA230197328T</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TABACCHI FRANZOI</t>
+          <t>BAR ORNELLA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1150,29 +1150,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EA560032007S</t>
+          <t>EA060088077R</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
+          <t>BAR PERDIGHE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EA560025127S</t>
+          <t>EA110017705R</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
+          <t>BAR PIT STOP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1184,12 +1184,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EA110017705R</t>
+          <t>EA570052178A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BAR PIT STOP</t>
+          <t>BAR PORTA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EA110123191R</t>
+          <t>EA230020700R</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BAR SAINT DENIS</t>
+          <t>BAR QUINTAVALLE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1218,29 +1218,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EA570052178A</t>
+          <t>EA230020700R</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BAR PORTA</t>
+          <t>BAR QUINTAVALLE_NTS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EA570047692R</t>
+          <t>EA110060727N</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAR GELATERIA ECLISSE</t>
+          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EA610201455R</t>
+          <t>EA110123191R</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LA RAVELLA</t>
+          <t>BAR SAINT DENIS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EA570008890A</t>
+          <t>EA570093813R</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LE PETIT BAR E CAFFE'</t>
+          <t>BAR SAN PIETRO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EA570025030A</t>
+          <t>EA560080006R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PASTICCERIA ERNANI</t>
+          <t>BAR SOFIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EA110213491R</t>
+          <t>EA570047109R</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WINNER CAFFE'</t>
+          <t>BAR SPORT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EA600008487R</t>
+          <t>EA560037045R</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAR ITALO</t>
+          <t>BAR SPORT (LC)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,46 +1337,46 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EA110061648W</t>
+          <t>EA060087417R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EA220084007M</t>
+          <t>EA060087417R</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BAR AL BOSCHETTO</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EA090004379E</t>
+          <t>EA010213090R</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
+          <t>BAR STAZIONE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1388,29 +1388,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EA570061069S</t>
+          <t>EA010021738R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
+          <t>BAR SUMALI'</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EA560022016R</t>
+          <t>EA110071158R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAR BALISIO</t>
+          <t>BAR TABACCHERIA EDEN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EA600145288K</t>
+          <t>EA110086976R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SALA SLOT VLT</t>
+          <t>BAR TABACCHI DI FRANCESCO SHI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1439,29 +1439,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EA190071960W</t>
+          <t>EA110019632A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ASD MASTER POOL CLUB</t>
+          <t>BAR TABACCHI DI MARIO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EA570067092K</t>
+          <t>EA110058238S</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BIG BAR</t>
+          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1473,29 +1473,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EA010021738R</t>
+          <t>EA570061069S</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAR SUMALI'</t>
+          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EA110075598A</t>
+          <t>EA610201455R</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NON SOLO FUMO</t>
+          <t>BAR TABACCHI LA RAVELLA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1507,29 +1507,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EA110229340M</t>
+          <t>EA590018902R</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
+          <t>BAR TABACCHI LADY WHITE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EA740113636H</t>
+          <t>EA590018902R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VILLAURBANA.NET</t>
+          <t>BAR TABACCHI LADY WHITE_NTS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1541,46 +1541,46 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EA560024683A</t>
+          <t>EA680081533R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BAR MANARA</t>
+          <t>BAR TOTAL_NTS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EA560082735A</t>
+          <t>EA730220299</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CAVALLI DIEGO</t>
+          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EA600023357O</t>
+          <t>EA560085800A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BREAK BAR - SERVICE</t>
+          <t>BAR VALLI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EA560106651R</t>
+          <t>EA050030669A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ELEFANTE CAFFE'</t>
+          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EA590042586T</t>
+          <t>EA570067092K</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LUCKY CAFFE'</t>
+          <t>BIG BAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EA570076231E</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FASHION CAFE'</t>
+          <t>BREAK BAR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1643,80 +1643,80 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EA580046885R</t>
+          <t>EA600023357O</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BAR FIORI</t>
+          <t>BREAK BAR - SERVICE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EA230020700R</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE</t>
+          <t>BREAK BAR_NTS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EA680081533R</t>
+          <t>EA060108406A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BAR TOTAL_NTS</t>
+          <t>C.R.A.L. MASUA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EA600056307R</t>
+          <t>EA060108406A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VAL DI RATT</t>
+          <t>C.R.A.L. MASUA_NTS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EA600147834M</t>
+          <t>EA110081007A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LA GARUFFA DI WU XIAOE</t>
+          <t>CAFE' NOIR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1728,29 +1728,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EA190071960W</t>
+          <t>EA580049855A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ASD MASTER POOL CLUB_NTS</t>
+          <t>CAFFE' 51</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EA570093813R</t>
+          <t>EA560072415A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BAR SAN PIETRO</t>
+          <t>CAFFE' IL BORGHETTO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,63 +1762,63 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EA060084328R</t>
+          <t>EA600009442A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BAR CENTRALE</t>
+          <t>CAFFE' PAINI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EA750227467B</t>
+          <t>EA560024520A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ISOLA CAFFE' SAMUGHEO</t>
+          <t>CAFFE' ROMA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EA750220260A</t>
+          <t>EA560061915O</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAPANNO 45 DI MATTIA COCCO</t>
+          <t>CAFFE' STAZIONE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EA750215537S</t>
+          <t>EA750220260A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TABACCHI PITZALIS</t>
+          <t>CAPANNO 45 DI MATTIA COCCO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1830,46 +1830,46 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EA750186167A</t>
+          <t>EA560082735A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KIKO CAFE' DI MURA FRANCESCO</t>
+          <t>CAVALLI DIEGO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EA060088077R</t>
+          <t>EA560068687A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BAR PERDIGHE</t>
+          <t>CIRCOLO FRATELLI FIGINI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EA740137695R</t>
+          <t>EA110230333G</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BAR DEL PARCO</t>
+          <t>COFFEE STOP DI CHEN JIANYANG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1881,97 +1881,97 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EA0600093414R</t>
+          <t>EA910210178A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BAR MARIO</t>
+          <t>DANG SRL - HI BAR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EA730220299</t>
+          <t>EA560205829D</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
+          <t>DEL ZOPPO DAVIS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EA060105360R</t>
+          <t>EA570053989R</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ANG&amp;LY CAFFE'</t>
+          <t>EDEN BAR TABACCHI GELATERIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EA060229230A</t>
+          <t>EA560032007S</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ASSOCIAZIONE PROMOZIONE SOCIALE NUOVO LOLLI CLUB_NTS</t>
+          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EA060227764C</t>
+          <t>EA560106651R</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NEW HOPE_NTS</t>
+          <t>ELEFANTE CAFFE'</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EA570008867A</t>
+          <t>EA570076231E</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AL CAFFERINO</t>
+          <t>FASHION CAFE'</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1983,29 +1983,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EA060108406A</t>
+          <t>EA580068587P</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA_NTS</t>
+          <t>FAX 13 DI CAPPELLATO FABIO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EA560205829D</t>
+          <t>EA090004379E</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DEL ZOPPO DAVIS</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2017,29 +2017,29 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EA110117489R</t>
+          <t>EA090004379E</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NUOVO BAR CENTRALE</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EA230188759R</t>
+          <t>EA110067815M</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BAR ITALIA (VE)</t>
+          <t>GREEN CAFE'</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EA560080006R</t>
+          <t>EA560076133A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BAR SOFIA</t>
+          <t>GUZZI CAFFE'</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EA050030669A</t>
+          <t>EA600145289K</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
+          <t>HAVANA SALA SLOT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2085,12 +2085,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EA090047671G</t>
+          <t>EA110047856S</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IZI PLAY GENOVA SARDEGNA</t>
+          <t>IL BRUCALIFFO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EA560014229R</t>
+          <t>EA610114587F</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BAR NORGE</t>
+          <t>IL VIZIO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,63 +2119,63 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EA570138375H</t>
+          <t>EA060228071B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SALA VIP</t>
+          <t>ISOLA C&amp;F SRL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EA110024352D</t>
+          <t>EA750227467B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
+          <t>ISOLA CAFFE' SAMUGHEO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EA560076133A</t>
+          <t>EA060229233B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GUZZI CAFFE'</t>
+          <t>ISOLA COFFE &amp; FOOD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EA230203099S</t>
+          <t>EA090047671G</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TABACCHI EDICOLA RIV. N.6</t>
+          <t>IZI PLAY GENOVA SARDEGNA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2187,29 +2187,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EA560061915O</t>
+          <t>EA750186167A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CAFFE' STAZIONE</t>
+          <t>KIKO CAFE' DI MURA FRANCESCO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EA560075507B</t>
+          <t>EA570008924W</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LA RIVIERASCA</t>
+          <t>L'INSOLITO POSTO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2221,29 +2221,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EA570010976A</t>
+          <t>EA600147834M</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MIMI' CAFE'</t>
+          <t>LA GARUFFA DI WU XIAOE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EA570026622N</t>
+          <t>EA560075507B</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PLANET BAR</t>
+          <t>LA RIVIERASCA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2255,46 +2255,46 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EA750225550C</t>
+          <t>EA570008890A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NEW BAR</t>
+          <t>LE PETIT BAR E CAFFE'</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EA060087417R</t>
+          <t>EA590042586T</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
+          <t>LUCKY CAFFE'</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EA910210178A</t>
+          <t>EA570010976A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DANG SRL - HI BAR</t>
+          <t>MIMI' CAFE'</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,97 +2306,97 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EA230163682H</t>
+          <t>EA750225550C</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RIV. TABACCHI N 5</t>
+          <t>NEW BAR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EA110067815M</t>
+          <t>EA750225550C</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GREEN CAFE'</t>
+          <t>NEW BAR_NTS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EA900206092R</t>
+          <t>EA060227764C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BAR BARAONDA DI JIN QINJING</t>
+          <t>NEW HOPE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EA060220578Q</t>
+          <t>EA060227764C</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ARBA MARCO</t>
+          <t>NEW HOPE_NTS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EA060108406A</t>
+          <t>EA580075762S</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA</t>
+          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EA580068587P</t>
+          <t>EA110075598A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FAX 13 DI CAPPELLATO FABIO</t>
+          <t>NON SOLO FUMO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EA600009349R</t>
+          <t>EA110117489R</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BAR HAVANA</t>
+          <t>NUOVO BAR CENTRALE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EA110065102A</t>
+          <t>EA230156447J</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PENNISI DAMIANO EZIO</t>
+          <t>OSTERIA VENEZIA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EA110060727N</t>
+          <t>EA560023440A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
+          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EA670043281S</t>
+          <t>EA570025030A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TABACCHERIA N. 10</t>
+          <t>PASTICCERIA ERNANI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EA110063817T</t>
+          <t>EA110147400D</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PICOLLO SILVIA RIV. N.7</t>
+          <t>PATCHOULI BAR &amp; MORE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EA670026114S</t>
+          <t>EA110065102A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TABACCHERIA ROSTAGNO</t>
+          <t>PENNISI DAMIANO EZIO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EA560023440A</t>
+          <t>EA110063817T</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
+          <t>PICOLLO SILVIA RIV. N.7</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EA690065910S</t>
+          <t>EA570026622N</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
+          <t>PLANET BAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EA560080343Y</t>
+          <t>EA110023653A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TOFE' CAFE'</t>
+          <t>PLAZA CAFE' - BIANCHI LUCA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EA610047253R</t>
+          <t>EA110014213S</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BAR JOLLY</t>
+          <t>POSTORINO GIUSEPPE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,12 +2578,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EA110014213S</t>
+          <t>EA570136910P</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>POSTORINO GIUSEPPE</t>
+          <t>PUB L' AFFRESCO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EA560072415A</t>
+          <t>EA560116579A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CAFFE' IL BORGHETTO</t>
+          <t>RISTORANTE TARTARUGA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EA610114587F</t>
+          <t>EA230163682H</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IL VIZIO</t>
+          <t>RIV. TABACCHI N 5</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,12 +2629,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EA560050362R</t>
+          <t>EA110013463S</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BAR 2 FANTI</t>
+          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,29 +2646,29 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EA060229230A</t>
+          <t>EA900030035H</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ASSOCIAZIONE PROMOZIONE SOCIALE NUOVO LOLLI CLUB</t>
+          <t>SALA GIOCHI PLAYERS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sisal Entertainment S.p.a.</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EA110058135S</t>
+          <t>EA600145288K</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TABACCHERIA ORCHIDEA VERDE</t>
+          <t>SALA SLOT VLT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,29 +2680,29 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EA560024228R</t>
+          <t>EA570138375H</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SOLE E LUNA DI CINZIA ZHANG</t>
+          <t>SALA VIP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EA570075631A</t>
+          <t>EA010227980A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TAVERNA DEL LUFF</t>
+          <t>SALLY BAR</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2714,46 +2714,46 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EA060227764C</t>
+          <t>EA560024228R</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NEW HOPE</t>
+          <t>SOLE E LUNA DI CINZIA ZHANG</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EA590017319S</t>
+          <t>EA110229340M</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
+          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EA900030035H</t>
+          <t>EA230005204S</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SALA GIOCHI PLAYERS</t>
+          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EA010213090R</t>
+          <t>EA110024352D</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BAR STAZIONE</t>
+          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EA110053037H</t>
+          <t>EA010220295S</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TABACCHERIA MORINI RENATO</t>
+          <t>TABACCHERIA AURORA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EA570136910P</t>
+          <t>EA110187005R</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PUB L' AFFRESCO</t>
+          <t>TABACCHERIA BACCO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EA600012344R</t>
+          <t>EA010067017S</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BAR LE TORRI</t>
+          <t>TABACCHERIA BAILONE ANDREA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EA910070191J</t>
+          <t>EA230092268R</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
+          <t>TABACCHERIA CARRER</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EA110047856S</t>
+          <t>EA110013488H</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IL BRUCALIFFO</t>
+          <t>TABACCHERIA CAVOUR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EA580049855A</t>
+          <t>EA560025127S</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CAFFE' 51</t>
+          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EA610007856A</t>
+          <t>EA110041885S</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ART CAFE' TABACCHERIA N. 2 - PRIVATIVA N. 2</t>
+          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2901,12 +2901,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EA110136204R</t>
+          <t>EA690065910S</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BAR ITALIA</t>
+          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EA230005204S</t>
+          <t>EA570014552S</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
+          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EA010220295S</t>
+          <t>EA230179267S</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TABACCHERIA AURORA</t>
+          <t>TABACCHERIA LEONARDO DA VINCI</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EA110026152R</t>
+          <t>EA110053037H</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BAR NUOVO MILLENNIO</t>
+          <t>TABACCHERIA MORINI RENATO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EA560024520A</t>
+          <t>EA670043281S</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CAFFE' ROMA</t>
+          <t>TABACCHERIA N. 10</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EA600009442A</t>
+          <t>EA110058135S</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CAFFE' PAINI</t>
+          <t>TABACCHERIA ORCHIDEA VERDE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EA610130067R</t>
+          <t>EA590017319S</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BAR CAFFETTERIA DOC</t>
+          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EA560041556A</t>
+          <t>EA670026114S</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BAR BARTH</t>
+          <t>TABACCHERIA ROSTAGNO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EA230092268R</t>
+          <t>EA570132577S</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TABACCHERIA CARRER</t>
+          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EA590018902R</t>
+          <t>EA910070191J</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE</t>
+          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EA110013488H</t>
+          <t>EA110057947A</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TABACCHERIA CAVOUR</t>
+          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EA110023653A</t>
+          <t>EA110043088F</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PLAZA CAFE' - BIANCHI LUCA</t>
+          <t>TABACCHI DI CHEN MAOXI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EA560116579A</t>
+          <t>EA230203099S</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RISTORANTE TARTARUGA</t>
+          <t>TABACCHI EDICOLA RIV. N.6</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EA570014552S</t>
+          <t>EA230014587S</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
+          <t>TABACCHI FRANZOI</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,29 +3139,29 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EA580075762S</t>
+          <t>EA750215537S</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
+          <t>TABACCHI PITZALIS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EA230179267S</t>
+          <t>EA570075631A</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TABACCHERIA LEONARDO DA VINCI</t>
+          <t>TAVERNA DEL LUFF</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EA110041885S</t>
+          <t>EA560080343Y</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
+          <t>TOFE' CAFE'</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EA010067017S</t>
+          <t>EA570011433R</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TABACCHERIA BAILONE ANDREA</t>
+          <t>ULTIMA PRIMA BAR TABACCHI</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,66 +3207,83 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA570011433R</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BREAK BAR</t>
+          <t>ULTIMA PRIMA BAR TABACCHI - SERVICE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EA110147400D</t>
+          <t>EA600056307R</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PATCHOULI BAR &amp; MORE</t>
+          <t>VAL DI RATT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EA010227980A</t>
+          <t>EA740113636H</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SALLY BAR</t>
+          <t>VILLAURBANA.NET</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EA110081007A</t>
+          <t>EA110061648W</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CAFE' NOIR</t>
+          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
+        <is>
+          <t>Snaitech Spa WG</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>EA110213491R</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>WINNER CAFFE'</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t>Snaitech Spa WG</t>
         </is>

--- a/elenco_locali.xlsx
+++ b/elenco_locali.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,46 +623,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EA560050362R</t>
+          <t>EA110230504A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAR 2 FANTI</t>
+          <t>BACIO BAR DI MENICANTI LIUDMYLA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EA220084007M</t>
+          <t>EA560050362R</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAR AL BOSCHETTO</t>
+          <t>BAR 2 FANTI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EA560022016R</t>
+          <t>EA220084007M</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAR BALISIO</t>
+          <t>BAR AL BOSCHETTO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EA900206092R</t>
+          <t>EA560022016R</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAR BARAONDA DI JIN QINJING</t>
+          <t>BAR BALISIO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EA560041556A</t>
+          <t>EA900206092R</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BAR BARTH</t>
+          <t>BAR BARAONDA DI JIN QINJING</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -708,12 +708,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EA610130067R</t>
+          <t>EA560041556A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAR CAFFETTERIA DOC</t>
+          <t>BAR BARTH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -725,29 +725,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EA060084328R</t>
+          <t>EA610130067R</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BAR CENTRALE</t>
+          <t>BAR CAFFETTERIA DOC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EA740137695R</t>
+          <t>EA060084328R</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAR DEL PARCO</t>
+          <t>BAR CENTRALE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -759,29 +759,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EA580114981R</t>
+          <t>EA740137695R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAR EDEN</t>
+          <t>BAR DEL PARCO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EA580046885R</t>
+          <t>EA580114981R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAR FIORI</t>
+          <t>BAR EDEN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -793,12 +793,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EA570047692R</t>
+          <t>EA580046885R</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BAR GELATERIA ECLISSE</t>
+          <t>BAR FIORI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EA600009349R</t>
+          <t>EA570047692R</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAR HAVANA</t>
+          <t>BAR GELATERIA ECLISSE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,17 +827,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EA910086595R</t>
+          <t>EA600009349R</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
+          <t>BAR HAVANA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
@@ -861,29 +861,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EA110136204R</t>
+          <t>EA910086595R</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAR ITALIA</t>
+          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EA230188759R</t>
+          <t>EA110136204R</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BAR ITALIA (VE)</t>
+          <t>BAR ITALIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EA600008487R</t>
+          <t>EA230188759R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAR ITALO</t>
+          <t>BAR ITALIA (VE)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EA610047253R</t>
+          <t>EA600008487R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAR JOLLY</t>
+          <t>BAR ITALO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EA570016040D</t>
+          <t>EA610047253R</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAR LA POSTA</t>
+          <t>BAR JOLLY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EA600012344R</t>
+          <t>EA570016040D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAR LE TORRI</t>
+          <t>BAR LA POSTA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -963,80 +963,80 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EA750192643R</t>
+          <t>EA600012344R</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAR M DI MELONI FRANCESCO</t>
+          <t>BAR LE TORRI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EA560024683A</t>
+          <t>EA750192643R</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BAR MANARA</t>
+          <t>BAR M DI MELONI FRANCESCO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EA0600093414R</t>
+          <t>EA560024683A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAR MARIO</t>
+          <t>BAR MANARA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EA010223483R</t>
+          <t>EA0600093414R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAR MISSISSIPI</t>
+          <t>BAR MARIO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EA900083204R</t>
+          <t>EA010223483R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BAR MULINO</t>
+          <t>BAR MISSISSIPI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1053,41 +1053,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BAR MULINO_NTS</t>
+          <t>BAR MULINO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EA560014229R</t>
+          <t>EA900083204R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BAR NORGE</t>
+          <t>BAR MULINO_NTS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EA110026152R</t>
+          <t>EA560014229R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BAR NUOVO MILLENNIO</t>
+          <t>BAR NORGE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EA230093288A</t>
+          <t>EA110026152R</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA</t>
+          <t>BAR NUOVO MILLENNIO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1121,75 +1121,75 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA - NTS</t>
+          <t>BAR OMBRALONGA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EA230197328T</t>
+          <t>EA230093288A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BAR ORNELLA</t>
+          <t>BAR OMBRALONGA - NTS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EA060088077R</t>
+          <t>EA230197328T</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BAR PERDIGHE</t>
+          <t>BAR ORNELLA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EA110017705R</t>
+          <t>EA060088077R</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BAR PIT STOP</t>
+          <t>BAR PERDIGHE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EA570052178A</t>
+          <t>EA110017705R</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BAR PORTA</t>
+          <t>BAR PIT STOP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EA230020700R</t>
+          <t>EA570052178A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE</t>
+          <t>BAR PORTA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1223,41 +1223,41 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE_NTS</t>
+          <t>BAR QUINTAVALLE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EA110060727N</t>
+          <t>EA230020700R</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
+          <t>BAR QUINTAVALLE_NTS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EA110123191R</t>
+          <t>EA110060727N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAR SAINT DENIS</t>
+          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EA570093813R</t>
+          <t>EA110123191R</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BAR SAN PIETRO</t>
+          <t>BAR SAINT DENIS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EA560080006R</t>
+          <t>EA570093813R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BAR SOFIA</t>
+          <t>BAR SAN PIETRO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EA570047109R</t>
+          <t>EA560080006R</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAR SPORT</t>
+          <t>BAR SOFIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EA560037045R</t>
+          <t>EA570047109R</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAR SPORT (LC)</t>
+          <t>BAR SPORT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EA060087417R</t>
+          <t>EA560037045R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
+          <t>BAR SPORT (LC)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
@@ -1359,75 +1359,75 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EA010213090R</t>
+          <t>EA060087417R</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BAR STAZIONE</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EA010021738R</t>
+          <t>EA010213090R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BAR SUMALI'</t>
+          <t>BAR STAZIONE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EA110071158R</t>
+          <t>EA010021738R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAR TABACCHERIA EDEN</t>
+          <t>BAR SUMALI'</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EA110086976R</t>
+          <t>EA110071158R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI FRANCESCO SHI</t>
+          <t>BAR TABACCHERIA EDEN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EA110019632A</t>
+          <t>EA110086976R</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI MARIO</t>
+          <t>BAR TABACCHI DI FRANCESCO SHI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1456,12 +1456,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EA110058238S</t>
+          <t>EA110019632A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
+          <t>BAR TABACCHI DI MARIO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EA570061069S</t>
+          <t>EA110058238S</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
+          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EA610201455R</t>
+          <t>EA570061069S</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LA RAVELLA</t>
+          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EA590018902R</t>
+          <t>EA610201455R</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE</t>
+          <t>BAR TABACCHI LA RAVELLA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1529,24 +1529,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE_NTS</t>
+          <t>BAR TABACCHI LADY WHITE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EA680081533R</t>
+          <t>EA590018902R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BAR TOTAL_NTS</t>
+          <t>BAR TABACCHI LADY WHITE_NTS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EA730220299</t>
+          <t>EA680081533R</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
+          <t>BAR TOTAL_NTS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1575,29 +1575,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EA560085800A</t>
+          <t>EA730220299</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BAR VALLI</t>
+          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EA050030669A</t>
+          <t>EA560085800A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
+          <t>BAR VALLI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EA570067092K</t>
+          <t>EA050030669A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BIG BAR</t>
+          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA570067092K</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BREAK BAR</t>
+          <t>BIG BAR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1643,51 +1643,51 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EA600023357O</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BREAK BAR - SERVICE</t>
+          <t>BREAK BAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA600023357O</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BREAK BAR_NTS</t>
+          <t>BREAK BAR - SERVICE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EA060108406A</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA</t>
+          <t>BREAK BAR_NTS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
@@ -1699,41 +1699,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA_NTS</t>
+          <t>C.R.A.L. MASUA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EA110081007A</t>
+          <t>EA060108406A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CAFE' NOIR</t>
+          <t>C.R.A.L. MASUA_NTS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EA580049855A</t>
+          <t>EA110081007A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CAFFE' 51</t>
+          <t>CAFE' NOIR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EA560072415A</t>
+          <t>EA580049855A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CAFFE' IL BORGHETTO</t>
+          <t>CAFFE' 51</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EA600009442A</t>
+          <t>EA560072415A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAFFE' PAINI</t>
+          <t>CAFFE' IL BORGHETTO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1779,12 +1779,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EA560024520A</t>
+          <t>EA600009442A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CAFFE' ROMA</t>
+          <t>CAFFE' PAINI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EA560061915O</t>
+          <t>EA560024520A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAFFE' STAZIONE</t>
+          <t>CAFFE' ROMA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1813,46 +1813,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EA750220260A</t>
+          <t>EA560061915O</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CAPANNO 45 DI MATTIA COCCO</t>
+          <t>CAFFE' STAZIONE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EA560082735A</t>
+          <t>EA750220260A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAVALLI DIEGO</t>
+          <t>CAPANNO 45 DI MATTIA COCCO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EA560068687A</t>
+          <t>EA560082735A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CIRCOLO FRATELLI FIGINI</t>
+          <t>CAVALLI DIEGO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1864,80 +1864,80 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EA110230333G</t>
+          <t>EA560068687A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COFFEE STOP DI CHEN JIANYANG</t>
+          <t>CIRCOLO FRATELLI FIGINI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EA910210178A</t>
+          <t>EA110230333G</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DANG SRL - HI BAR</t>
+          <t>COFFEE STOP DI CHEN JIANYANG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EA560205829D</t>
+          <t>EA910210178A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DEL ZOPPO DAVIS</t>
+          <t>DANG SRL - HI BAR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EA570053989R</t>
+          <t>EA560205829D</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EDEN BAR TABACCHI GELATERIA</t>
+          <t>DEL ZOPPO DAVIS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EA560032007S</t>
+          <t>EA570053989R</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
+          <t>EDEN BAR TABACCHI GELATERIA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EA560106651R</t>
+          <t>EA560032007S</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ELEFANTE CAFFE'</t>
+          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EA570076231E</t>
+          <t>EA560106651R</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FASHION CAFE'</t>
+          <t>ELEFANTE CAFFE'</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1983,12 +1983,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EA580068587P</t>
+          <t>EA570076231E</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FAX 13 DI CAPPELLATO FABIO</t>
+          <t>FASHION CAFE'</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EA090004379E</t>
+          <t>EA580068587P</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
+          <t>FAX 13 DI CAPPELLATO FABIO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2022,41 +2022,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EA110067815M</t>
+          <t>EA090004379E</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GREEN CAFE'</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EA560076133A</t>
+          <t>EA110067815M</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GUZZI CAFFE'</t>
+          <t>GREEN CAFE'</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EA600145289K</t>
+          <t>EA560076133A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HAVANA SALA SLOT</t>
+          <t>GUZZI CAFFE'</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2085,12 +2085,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EA110047856S</t>
+          <t>EA600145289K</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IL BRUCALIFFO</t>
+          <t>HAVANA SALA SLOT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EA610114587F</t>
+          <t>EA110047856S</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IL VIZIO</t>
+          <t>IL BRUCALIFFO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,29 +2119,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EA060228071B</t>
+          <t>EA610114587F</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISOLA C&amp;F SRL</t>
+          <t>IL VIZIO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EA750227467B</t>
+          <t>EA060228071B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ISOLA CAFFE' SAMUGHEO</t>
+          <t>ISOLA C&amp;F SRL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EA060229233B</t>
+          <t>EA750227467B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ISOLA COFFE &amp; FOOD</t>
+          <t>ISOLA CAFFE' SAMUGHEO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,97 +2170,97 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EA090047671G</t>
+          <t>EA060229233B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IZI PLAY GENOVA SARDEGNA</t>
+          <t>ISOLA COFFE &amp; FOOD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EA750186167A</t>
+          <t>EA090047671G</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KIKO CAFE' DI MURA FRANCESCO</t>
+          <t>IZI PLAY GENOVA SARDEGNA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EA570008924W</t>
+          <t>EA750186167A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>L'INSOLITO POSTO</t>
+          <t>KIKO CAFE' DI MURA FRANCESCO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EA600147834M</t>
+          <t>EA570008924W</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LA GARUFFA DI WU XIAOE</t>
+          <t>L'INSOLITO POSTO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EA560075507B</t>
+          <t>EA600147834M</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LA RIVIERASCA</t>
+          <t>LA GARUFFA DI WU XIAOE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EA570008890A</t>
+          <t>EA560075507B</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LE PETIT BAR E CAFFE'</t>
+          <t>LA RIVIERASCA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EA590042586T</t>
+          <t>EA570008890A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LUCKY CAFFE'</t>
+          <t>LE PETIT BAR E CAFFE'</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EA570010976A</t>
+          <t>EA590042586T</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MIMI' CAFE'</t>
+          <t>LUCKY CAFFE'</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,17 +2306,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EA750225550C</t>
+          <t>EA570010976A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NEW BAR</t>
+          <t>MIMI' CAFE'</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
@@ -2328,29 +2328,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NEW BAR_NTS</t>
+          <t>NEW BAR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EA060227764C</t>
+          <t>EA750225550C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NEW HOPE</t>
+          <t>NEW BAR_NTS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
@@ -2362,41 +2362,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NEW HOPE_NTS</t>
+          <t>NEW HOPE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EA580075762S</t>
+          <t>EA060227764C</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
+          <t>NEW HOPE_NTS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EA110075598A</t>
+          <t>EA580075762S</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NON SOLO FUMO</t>
+          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EA110117489R</t>
+          <t>EA110075598A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NUOVO BAR CENTRALE</t>
+          <t>NON SOLO FUMO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EA230156447J</t>
+          <t>EA110117489R</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OSTERIA VENEZIA</t>
+          <t>NUOVO BAR CENTRALE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EA560023440A</t>
+          <t>EA230156447J</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
+          <t>OSTERIA VENEZIA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EA570025030A</t>
+          <t>EA560023440A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PASTICCERIA ERNANI</t>
+          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EA110147400D</t>
+          <t>EA570025030A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PATCHOULI BAR &amp; MORE</t>
+          <t>PASTICCERIA ERNANI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EA110065102A</t>
+          <t>EA110147400D</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PENNISI DAMIANO EZIO</t>
+          <t>PATCHOULI BAR &amp; MORE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EA110063817T</t>
+          <t>EA110065102A</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PICOLLO SILVIA RIV. N.7</t>
+          <t>PENNISI DAMIANO EZIO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EA570026622N</t>
+          <t>EA110063817T</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PLANET BAR</t>
+          <t>PICOLLO SILVIA RIV. N.7</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EA110023653A</t>
+          <t>EA570026622N</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PLAZA CAFE' - BIANCHI LUCA</t>
+          <t>PLANET BAR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EA110014213S</t>
+          <t>EA110023653A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>POSTORINO GIUSEPPE</t>
+          <t>PLAZA CAFE' - BIANCHI LUCA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,12 +2578,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EA570136910P</t>
+          <t>EA110014213S</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PUB L' AFFRESCO</t>
+          <t>POSTORINO GIUSEPPE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EA560116579A</t>
+          <t>EA570136910P</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RISTORANTE TARTARUGA</t>
+          <t>PUB L' AFFRESCO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EA230163682H</t>
+          <t>EA560116579A</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RIV. TABACCHI N 5</t>
+          <t>RISTORANTE TARTARUGA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,12 +2629,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EA110013463S</t>
+          <t>EA230163682H</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
+          <t>RIV. TABACCHI N 5</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EA900030035H</t>
+          <t>EA110013463S</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SALA GIOCHI PLAYERS</t>
+          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EA600145288K</t>
+          <t>EA900030035H</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SALA SLOT VLT</t>
+          <t>SALA GIOCHI PLAYERS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,46 +2680,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EA570138375H</t>
+          <t>EA600145288K</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SALA VIP</t>
+          <t>SALA SLOT VLT</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EA010227980A</t>
+          <t>EA570138375H</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SALLY BAR</t>
+          <t>SALA VIP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EA560024228R</t>
+          <t>EA010227980A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SOLE E LUNA DI CINZIA ZHANG</t>
+          <t>SALLY BAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2731,46 +2731,46 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EA110229340M</t>
+          <t>EA560024228R</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
+          <t>SOLE E LUNA DI CINZIA ZHANG</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EA230005204S</t>
+          <t>EA110229340M</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
+          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EA110024352D</t>
+          <t>EA230005204S</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
+          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EA010220295S</t>
+          <t>EA110024352D</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TABACCHERIA AURORA</t>
+          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EA110187005R</t>
+          <t>EA010220295S</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TABACCHERIA BACCO</t>
+          <t>TABACCHERIA AURORA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EA010067017S</t>
+          <t>EA110187005R</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TABACCHERIA BAILONE ANDREA</t>
+          <t>TABACCHERIA BACCO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EA230092268R</t>
+          <t>EA010067017S</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TABACCHERIA CARRER</t>
+          <t>TABACCHERIA BAILONE ANDREA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EA110013488H</t>
+          <t>EA230092268R</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TABACCHERIA CAVOUR</t>
+          <t>TABACCHERIA CARRER</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EA560025127S</t>
+          <t>EA110013488H</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
+          <t>TABACCHERIA CAVOUR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EA110041885S</t>
+          <t>EA560025127S</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
+          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2901,12 +2901,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EA690065910S</t>
+          <t>EA110041885S</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
+          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EA570014552S</t>
+          <t>EA690065910S</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
+          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EA230179267S</t>
+          <t>EA570014552S</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TABACCHERIA LEONARDO DA VINCI</t>
+          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EA110053037H</t>
+          <t>EA230179267S</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TABACCHERIA MORINI RENATO</t>
+          <t>TABACCHERIA LEONARDO DA VINCI</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EA670043281S</t>
+          <t>EA110053037H</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TABACCHERIA N. 10</t>
+          <t>TABACCHERIA MORINI RENATO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EA110058135S</t>
+          <t>EA670043281S</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TABACCHERIA ORCHIDEA VERDE</t>
+          <t>TABACCHERIA N. 10</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EA590017319S</t>
+          <t>EA110058135S</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
+          <t>TABACCHERIA ORCHIDEA VERDE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EA670026114S</t>
+          <t>EA590017319S</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TABACCHERIA ROSTAGNO</t>
+          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EA570132577S</t>
+          <t>EA670026114S</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
+          <t>TABACCHERIA ROSTAGNO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EA910070191J</t>
+          <t>EA570132577S</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
+          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EA110057947A</t>
+          <t>EA910070191J</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
+          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EA110043088F</t>
+          <t>EA110057947A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TABACCHI DI CHEN MAOXI</t>
+          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EA230203099S</t>
+          <t>EA110043088F</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TABACCHI EDICOLA RIV. N.6</t>
+          <t>TABACCHI DI CHEN MAOXI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EA230014587S</t>
+          <t>EA230203099S</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TABACCHI FRANZOI</t>
+          <t>TABACCHI EDICOLA RIV. N.6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,46 +3139,46 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EA750215537S</t>
+          <t>EA230014587S</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TABACCHI PITZALIS</t>
+          <t>TABACCHI FRANZOI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EA570075631A</t>
+          <t>EA750215537S</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TAVERNA DEL LUFF</t>
+          <t>TABACCHI PITZALIS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EA560080343Y</t>
+          <t>EA570075631A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TOFE' CAFE'</t>
+          <t>TAVERNA DEL LUFF</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EA570011433R</t>
+          <t>EA560080343Y</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ULTIMA PRIMA BAR TABACCHI</t>
+          <t>TOFE' CAFE'</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3212,24 +3212,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ULTIMA PRIMA BAR TABACCHI - SERVICE</t>
+          <t>ULTIMA PRIMA BAR TABACCHI</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EA600056307R</t>
+          <t>EA570011433R</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>VAL DI RATT</t>
+          <t>ULTIMA PRIMA BAR TABACCHI - SERVICE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3241,49 +3241,66 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EA740113636H</t>
+          <t>EA600056307R</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>VILLAURBANA.NET</t>
+          <t>VAL DI RATT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EA110061648W</t>
+          <t>EA740113636H</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
+          <t>VILLAURBANA.NET</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>EA110061648W</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Snaitech Spa WG</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
           <t>EA110213491R</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>WINNER CAFFE'</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>Snaitech Spa WG</t>
         </is>

--- a/elenco_locali.xlsx
+++ b/elenco_locali.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,46 +640,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EA560050362R</t>
+          <t>EA110230504A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAR 2 FANTI</t>
+          <t>BACIO BAR DI MENICANTI LIUDMYLA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EA220084007M</t>
+          <t>EA560050362R</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAR AL BOSCHETTO</t>
+          <t>BAR 2 FANTI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EA560022016R</t>
+          <t>EA220084007M</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAR BALISIO</t>
+          <t>BAR AL BOSCHETTO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EA900206092R</t>
+          <t>EA560022016R</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BAR BARAONDA DI JIN QINJING</t>
+          <t>BAR BALISIO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -708,12 +708,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EA560041556A</t>
+          <t>EA900206092R</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAR BARTH</t>
+          <t>BAR BARAONDA DI JIN QINJING</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EA610130067R</t>
+          <t>EA560041556A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BAR CAFFETTERIA DOC</t>
+          <t>BAR BARTH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -742,29 +742,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EA060084328R</t>
+          <t>EA610130067R</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAR CENTRALE</t>
+          <t>BAR CAFFETTERIA DOC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EA740137695R</t>
+          <t>EA060084328R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAR DEL PARCO</t>
+          <t>BAR CENTRALE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -776,29 +776,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EA580114981R</t>
+          <t>EA740137695R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAR EDEN</t>
+          <t>BAR DEL PARCO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EA580046885R</t>
+          <t>EA580114981R</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BAR FIORI</t>
+          <t>BAR EDEN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EA570047692R</t>
+          <t>EA580046885R</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAR GELATERIA ECLISSE</t>
+          <t>BAR FIORI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EA600009349R</t>
+          <t>EA570047692R</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BAR HAVANA</t>
+          <t>BAR GELATERIA ECLISSE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EA910086595R</t>
+          <t>EA600009349R</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
+          <t>BAR HAVANA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -878,12 +878,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EA110136204R</t>
+          <t>EA910086595R</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BAR ITALIA</t>
+          <t>BAR HELLAS DI DAI JUNSHAN_NTS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EA230188759R</t>
+          <t>EA110136204R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BAR ITALIA (VE)</t>
+          <t>BAR ITALIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EA600008487R</t>
+          <t>EA230188759R</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAR ITALO</t>
+          <t>BAR ITALIA (VE)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EA610047253R</t>
+          <t>EA600008487R</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BAR JOLLY</t>
+          <t>BAR ITALO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,12 +946,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EA570016040D</t>
+          <t>EA610047253R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAR LA POSTA</t>
+          <t>BAR JOLLY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EA600012344R</t>
+          <t>EA570016040D</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAR LE TORRI</t>
+          <t>BAR LA POSTA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -980,80 +980,80 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EA750192643R</t>
+          <t>EA600012344R</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BAR M DI MELONI FRANCESCO</t>
+          <t>BAR LE TORRI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EA560024683A</t>
+          <t>EA750192643R</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAR MANARA</t>
+          <t>BAR M DI MELONI FRANCESCO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EA0600093414R</t>
+          <t>EA560024683A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAR MARIO</t>
+          <t>BAR MANARA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EA010223483R</t>
+          <t>EA0600093414R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BAR MISSISSIPI</t>
+          <t>BAR MARIO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EA900083204R</t>
+          <t>EA010223483R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BAR MULINO</t>
+          <t>BAR MISSISSIPI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1070,41 +1070,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BAR MULINO_NTS</t>
+          <t>BAR MULINO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EA560014229R</t>
+          <t>EA900083204R</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BAR NORGE</t>
+          <t>BAR MULINO_NTS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EA110026152R</t>
+          <t>EA560014229R</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BAR NUOVO MILLENNIO</t>
+          <t>BAR NORGE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1116,12 +1116,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EA230093288A</t>
+          <t>EA110026152R</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA</t>
+          <t>BAR NUOVO MILLENNIO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1138,75 +1138,75 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BAR OMBRALONGA - NTS</t>
+          <t>BAR OMBRALONGA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EA230197328T</t>
+          <t>EA230093288A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BAR ORNELLA</t>
+          <t>BAR OMBRALONGA - NTS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EA060088077R</t>
+          <t>EA230197328T</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BAR PERDIGHE</t>
+          <t>BAR ORNELLA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EA110017705R</t>
+          <t>EA060088077R</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BAR PIT STOP</t>
+          <t>BAR PERDIGHE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EA570052178A</t>
+          <t>EA110017705R</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BAR PORTA</t>
+          <t>BAR PIT STOP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EA230020700R</t>
+          <t>EA570052178A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE</t>
+          <t>BAR PORTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1240,41 +1240,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAR QUINTAVALLE_NTS</t>
+          <t>BAR QUINTAVALLE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EA110060727N</t>
+          <t>EA230020700R</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
+          <t>BAR QUINTAVALLE_NTS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EA110123191R</t>
+          <t>EA110060727N</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BAR SAINT DENIS</t>
+          <t>BAR RIVA DUE DI FUMAGALLI IVAN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EA570093813R</t>
+          <t>EA110123191R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BAR SAN PIETRO</t>
+          <t>BAR SAINT DENIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EA560080006R</t>
+          <t>EA570093813R</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BAR SOFIA</t>
+          <t>BAR SAN PIETRO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EA570047109R</t>
+          <t>EA560080006R</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAR SPORT</t>
+          <t>BAR SOFIA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EA560037045R</t>
+          <t>EA570047109R</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BAR SPORT (LC)</t>
+          <t>BAR SPORT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1354,17 +1354,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EA060087417R</t>
+          <t>EA560037045R</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
+          <t>BAR SPORT (LC)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
@@ -1376,75 +1376,75 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EA010213090R</t>
+          <t>EA060087417R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BAR STAZIONE</t>
+          <t>BAR SPORT DI OGNO LORENZO &amp; C. SNC_NTS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EA010021738R</t>
+          <t>EA010213090R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAR SUMALI'</t>
+          <t>BAR STAZIONE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EA110071158R</t>
+          <t>EA010021738R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAR TABACCHERIA EDEN</t>
+          <t>BAR SUMALI'</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EA110086976R</t>
+          <t>EA110071158R</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI FRANCESCO SHI</t>
+          <t>BAR TABACCHERIA EDEN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1456,12 +1456,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EA110019632A</t>
+          <t>EA110086976R</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI MARIO</t>
+          <t>BAR TABACCHI DI FRANCESCO SHI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EA110058238S</t>
+          <t>EA110019632A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
+          <t>BAR TABACCHI DI MARIO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EA570061069S</t>
+          <t>EA110058238S</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
+          <t>BAR TABACCHI DI XU DANIELE QI LONG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EA610201455R</t>
+          <t>EA570061069S</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LA RAVELLA</t>
+          <t>BAR TABACCHI EDICOLA GEROSA MORENO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1524,12 +1524,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EA590018902R</t>
+          <t>EA610201455R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE</t>
+          <t>BAR TABACCHI LA RAVELLA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BAR TABACCHI LADY WHITE_NTS</t>
+          <t>BAR TABACCHI LADY WHITE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EA680081533R</t>
+          <t>EA590018902R</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BAR TOTAL_NTS</t>
+          <t>BAR TABACCHI LADY WHITE_NTS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EA730220299</t>
+          <t>EA680081533R</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
+          <t>BAR TOTAL_NTS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1592,29 +1592,29 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EA560085800A</t>
+          <t>EA730220299</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BAR VALLI</t>
+          <t>BAR TOTO S.N.C MACIS E CARBONI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EA050030669A</t>
+          <t>EA560085800A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
+          <t>BAR VALLI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EA570067092K</t>
+          <t>EA050030669A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BIG BAR</t>
+          <t>BERNY CAFE' DI MOSCA CLAUDIA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA570067092K</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BREAK BAR</t>
+          <t>BIG BAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1660,51 +1660,51 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EA600023357O</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BREAK BAR - SERVICE</t>
+          <t>BREAK BAR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EA110056963O</t>
+          <t>EA600023357O</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BREAK BAR_NTS</t>
+          <t>BREAK BAR - SERVICE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EA060108406A</t>
+          <t>EA110056963O</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA</t>
+          <t>BREAK BAR_NTS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
@@ -1716,41 +1716,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C.R.A.L. MASUA_NTS</t>
+          <t>C.R.A.L. MASUA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EA110081007A</t>
+          <t>EA060108406A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CAFE' NOIR</t>
+          <t>C.R.A.L. MASUA_NTS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EA580049855A</t>
+          <t>EA110081007A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CAFFE' 51</t>
+          <t>CAFE' NOIR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EA560072415A</t>
+          <t>EA580049855A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAFFE' IL BORGHETTO</t>
+          <t>CAFFE' 51</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1779,12 +1779,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EA600009442A</t>
+          <t>EA560072415A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CAFFE' PAINI</t>
+          <t>CAFFE' IL BORGHETTO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EA560024520A</t>
+          <t>EA600009442A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAFFE' ROMA</t>
+          <t>CAFFE' PAINI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EA560061915O</t>
+          <t>EA560024520A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CAFFE' STAZIONE</t>
+          <t>CAFFE' ROMA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1830,46 +1830,46 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EA750220260A</t>
+          <t>EA560061915O</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAPANNO 45 DI MATTIA COCCO</t>
+          <t>CAFFE' STAZIONE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EA560082735A</t>
+          <t>EA750220260A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CAVALLI DIEGO</t>
+          <t>CAPANNO 45 DI MATTIA COCCO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EA560068687A</t>
+          <t>EA560082735A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CIRCOLO FRATELLI FIGINI</t>
+          <t>CAVALLI DIEGO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1881,80 +1881,80 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EA110230333G</t>
+          <t>EA560068687A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COFFEE STOP DI CHEN JIANYANG</t>
+          <t>CIRCOLO FRATELLI FIGINI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EA910210178A</t>
+          <t>EA110230333G</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DANG SRL - HI BAR</t>
+          <t>COFFEE STOP DI CHEN JIANYANG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EA560205829D</t>
+          <t>EA910210178A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DEL ZOPPO DAVIS</t>
+          <t>DANG SRL - HI BAR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EA570053989R</t>
+          <t>EA560205829D</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EDEN BAR TABACCHI GELATERIA</t>
+          <t>DEL ZOPPO DAVIS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EA560032007S</t>
+          <t>EA570053989R</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
+          <t>EDEN BAR TABACCHI GELATERIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EA560106651R</t>
+          <t>EA560032007S</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ELEFANTE CAFFE'</t>
+          <t>EDICOLA VILLAGGIO DEGLI SPOSI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1983,12 +1983,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EA570076231E</t>
+          <t>EA560106651R</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FASHION CAFE'</t>
+          <t>ELEFANTE CAFFE'</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EA580068587P</t>
+          <t>EA570076231E</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FAX 13 DI CAPPELLATO FABIO</t>
+          <t>FASHION CAFE'</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EA090004379E</t>
+          <t>EA580068587P</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
+          <t>FAX 13 DI CAPPELLATO FABIO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2039,41 +2039,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EA110067815M</t>
+          <t>EA090004379E</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GREEN CAFE'</t>
+          <t>FRASH S.A.S. DI FRASCERRA MATTIA E C._NTS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EA560076133A</t>
+          <t>EA110067815M</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GUZZI CAFFE'</t>
+          <t>GREEN CAFE'</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2085,12 +2085,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EA600145289K</t>
+          <t>EA560076133A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HAVANA SALA SLOT</t>
+          <t>GUZZI CAFFE'</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EA110047856S</t>
+          <t>EA600145289K</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IL BRUCALIFFO</t>
+          <t>HAVANA SALA SLOT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EA610114587F</t>
+          <t>EA110047856S</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IL VIZIO</t>
+          <t>IL BRUCALIFFO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2136,29 +2136,29 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EA060228071B</t>
+          <t>EA610114587F</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ISOLA C&amp;F SRL</t>
+          <t>IL VIZIO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EA750227467B</t>
+          <t>EA060228071B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ISOLA CAFFE' SAMUGHEO</t>
+          <t>ISOLA C&amp;F SRL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EA060229233B</t>
+          <t>EA750227467B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISOLA COFFE &amp; FOOD</t>
+          <t>ISOLA CAFFE' SAMUGHEO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2187,97 +2187,97 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EA090047671G</t>
+          <t>EA060229233B</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IZI PLAY GENOVA SARDEGNA</t>
+          <t>ISOLA COFFE &amp; FOOD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EA750186167A</t>
+          <t>EA090047671G</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KIKO CAFE' DI MURA FRANCESCO</t>
+          <t>IZI PLAY GENOVA SARDEGNA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EA570008924W</t>
+          <t>EA750186167A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>L'INSOLITO POSTO</t>
+          <t>KIKO CAFE' DI MURA FRANCESCO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EA600147834M</t>
+          <t>EA570008924W</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LA GARUFFA DI WU XIAOE</t>
+          <t>L'INSOLITO POSTO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EA560075507B</t>
+          <t>EA600147834M</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LA RIVIERASCA</t>
+          <t>LA GARUFFA DI WU XIAOE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EA570008890A</t>
+          <t>EA560075507B</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LE PETIT BAR E CAFFE'</t>
+          <t>LA RIVIERASCA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EA590042586T</t>
+          <t>EA570008890A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LUCKY CAFFE'</t>
+          <t>LE PETIT BAR E CAFFE'</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,12 +2306,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EA570010976A</t>
+          <t>EA590042586T</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MIMI' CAFE'</t>
+          <t>LUCKY CAFFE'</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2323,17 +2323,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EA750225550C</t>
+          <t>EA570010976A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NEW BAR</t>
+          <t>MIMI' CAFE'</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
@@ -2345,29 +2345,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NEW BAR_NTS</t>
+          <t>NEW BAR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EA060227764C</t>
+          <t>EA750225550C</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NEW HOPE</t>
+          <t>NEW BAR_NTS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Global Starnet</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
@@ -2379,41 +2379,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NEW HOPE_NTS</t>
+          <t>NEW HOPE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Global Starnet</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EA580075762S</t>
+          <t>EA060227764C</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
+          <t>NEW HOPE_NTS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EA110075598A</t>
+          <t>EA580075762S</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NON SOLO FUMO</t>
+          <t>NIPOS TABACCHI DI BRANCHINI EMANUEL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EA110117489R</t>
+          <t>EA110075598A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NUOVO BAR CENTRALE</t>
+          <t>NON SOLO FUMO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EA230156447J</t>
+          <t>EA110117489R</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OSTERIA VENEZIA</t>
+          <t>NUOVO BAR CENTRALE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EA560023440A</t>
+          <t>EA230156447J</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
+          <t>OSTERIA VENEZIA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EA570025030A</t>
+          <t>EA560023440A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PASTICCERIA ERNANI</t>
+          <t>PAMPI CAFE' DI BRAMBILLA ANDREA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EA110147400D</t>
+          <t>EA570025030A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PATCHOULI BAR &amp; MORE</t>
+          <t>PASTICCERIA ERNANI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EA110065102A</t>
+          <t>EA110147400D</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PENNISI DAMIANO EZIO</t>
+          <t>PATCHOULI BAR &amp; MORE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EA110063817T</t>
+          <t>EA110065102A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PICOLLO SILVIA RIV. N.7</t>
+          <t>PENNISI DAMIANO EZIO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EA570026622N</t>
+          <t>EA110063817T</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PLANET BAR</t>
+          <t>PICOLLO SILVIA RIV. N.7</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EA110023653A</t>
+          <t>EA570026622N</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PLAZA CAFE' - BIANCHI LUCA</t>
+          <t>PLANET BAR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,12 +2578,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EA110014213S</t>
+          <t>EA110023653A</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>POSTORINO GIUSEPPE</t>
+          <t>PLAZA CAFE' - BIANCHI LUCA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EA570136910P</t>
+          <t>EA110014213S</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PUB L' AFFRESCO</t>
+          <t>POSTORINO GIUSEPPE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EA560116579A</t>
+          <t>EA570136910P</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RISTORANTE TARTARUGA</t>
+          <t>PUB L' AFFRESCO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,12 +2629,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EA230163682H</t>
+          <t>EA560116579A</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RIV. TABACCHI N 5</t>
+          <t>RISTORANTE TARTARUGA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EA110013463S</t>
+          <t>EA230163682H</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
+          <t>RIV. TABACCHI N 5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EA900030035H</t>
+          <t>EA110013463S</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SALA GIOCHI PLAYERS</t>
+          <t>RUYI CAFE' - BAR TABACCHI DI ZHENG ALESSIA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EA600145288K</t>
+          <t>EA900030035H</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SALA SLOT VLT</t>
+          <t>SALA GIOCHI PLAYERS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,46 +2697,46 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EA570138375H</t>
+          <t>EA600145288K</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SALA VIP</t>
+          <t>SALA SLOT VLT</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EA010227980A</t>
+          <t>EA570138375H</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SALLY BAR</t>
+          <t>SALA VIP</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EA560024228R</t>
+          <t>EA010227980A</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SOLE E LUNA DI CINZIA ZHANG</t>
+          <t>SALLY BAR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2748,46 +2748,46 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EA110229340M</t>
+          <t>EA560024228R</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
+          <t>SOLE E LUNA DI CINZIA ZHANG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EA230005204S</t>
+          <t>EA110229340M</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
+          <t>STAZIONE SERVIZIO GETOIL MANAH</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EA110024352D</t>
+          <t>EA230005204S</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
+          <t>TAB. BURATO ANTONIETTA RIV. 8</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EA010220295S</t>
+          <t>EA110024352D</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TABACCHERIA AURORA</t>
+          <t>TABACCHERIA 1081 DI CARBONE SANDRO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EA110187005R</t>
+          <t>EA010220295S</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TABACCHERIA BACCO</t>
+          <t>TABACCHERIA AURORA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EA010067017S</t>
+          <t>EA110187005R</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TABACCHERIA BAILONE ANDREA</t>
+          <t>TABACCHERIA BACCO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,12 +2850,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EA230092268R</t>
+          <t>EA010067017S</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TABACCHERIA CARRER</t>
+          <t>TABACCHERIA BAILONE ANDREA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2867,12 +2867,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EA110013488H</t>
+          <t>EA230092268R</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TABACCHERIA CAVOUR</t>
+          <t>TABACCHERIA CARRER</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EA560025127S</t>
+          <t>EA110013488H</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
+          <t>TABACCHERIA CAVOUR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2901,12 +2901,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EA110041885S</t>
+          <t>EA560025127S</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
+          <t>TABACCHERIA DE ORGNA' DI LIU GUO KAI OSCAR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EA690065910S</t>
+          <t>EA110041885S</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
+          <t>TABACCHERIA DI MANOSPERTI PATRIZIA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EA570014552S</t>
+          <t>EA690065910S</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
+          <t>TABACCHERIA DI MONTAROLO DANIELE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EA230179267S</t>
+          <t>EA570014552S</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TABACCHERIA LEONARDO DA VINCI</t>
+          <t>TABACCHERIA LA POSTA DI SCUDERI SIMONA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EA110053037H</t>
+          <t>EA230179267S</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TABACCHERIA MORINI RENATO</t>
+          <t>TABACCHERIA LEONARDO DA VINCI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EA670043281S</t>
+          <t>EA110053037H</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TABACCHERIA N. 10</t>
+          <t>TABACCHERIA MORINI RENATO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EA110058135S</t>
+          <t>EA670043281S</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TABACCHERIA ORCHIDEA VERDE</t>
+          <t>TABACCHERIA N. 10</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EA590017319S</t>
+          <t>EA110058135S</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
+          <t>TABACCHERIA ORCHIDEA VERDE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EA670026114S</t>
+          <t>EA590017319S</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TABACCHERIA ROSTAGNO</t>
+          <t>TABACCHERIA RICEVITORIA VISENTINI PAOLO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EA570132577S</t>
+          <t>EA670026114S</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
+          <t>TABACCHERIA ROSTAGNO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EA910070191J</t>
+          <t>EA570132577S</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
+          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EA110057947A</t>
+          <t>EA910070191J</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
+          <t>TABACCHERIA VENETA DI PALMA ALESSANDRA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EA110043088F</t>
+          <t>EA110057947A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TABACCHI DI CHEN MAOXI</t>
+          <t>TABACCHI DELLA PIAZZA DI LIN ELENA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EA230203099S</t>
+          <t>EA110043088F</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TABACCHI EDICOLA RIV. N.6</t>
+          <t>TABACCHI DI CHEN MAOXI</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EA230014587S</t>
+          <t>EA230203099S</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TABACCHI FRANZOI</t>
+          <t>TABACCHI EDICOLA RIV. N.6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3156,46 +3156,46 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EA750215537S</t>
+          <t>EA230014587S</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TABACCHI PITZALIS</t>
+          <t>TABACCHI FRANZOI</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EA570075631A</t>
+          <t>EA750215537S</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TAVERNA DEL LUFF</t>
+          <t>TABACCHI PITZALIS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EA560080343Y</t>
+          <t>EA570075631A</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TOFE' CAFE'</t>
+          <t>TAVERNA DEL LUFF</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EA570011433R</t>
+          <t>EA560080343Y</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ULTIMA PRIMA BAR TABACCHI</t>
+          <t>TOFE' CAFE'</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3229,24 +3229,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ULTIMA PRIMA BAR TABACCHI - SERVICE</t>
+          <t>ULTIMA PRIMA BAR TABACCHI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SNAITECH SPA</t>
+          <t>Snaitech Spa WG</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EA600056307R</t>
+          <t>EA570011433R</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>VAL DI RATT</t>
+          <t>ULTIMA PRIMA BAR TABACCHI - SERVICE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3258,49 +3258,66 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EA740113636H</t>
+          <t>EA600056307R</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>VILLAURBANA.NET</t>
+          <t>VAL DI RATT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NTS Networks</t>
+          <t>SNAITECH SPA</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EA110061648W</t>
+          <t>EA740113636H</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
+          <t>VILLAURBANA.NET</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Snaitech Spa WG</t>
+          <t>NTS Networks</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>EA110061648W</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>WG TABACCHERIA CHIAPPETTA DEBORA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Snaitech Spa WG</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>EA110213491R</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>WINNER CAFFE'</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Snaitech Spa WG</t>
         </is>
